--- a/Ryan/Dataset/kepadatanpenduduksby24.xlsx
+++ b/Ryan/Dataset/kepadatanpenduduksby24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ryan\Documents\tugas_akhir\tugas_akhir\Ryan\Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6864BB5F-FB36-40B0-81E6-E5DDFFD6A339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA05FF3E-5C41-4D1E-BDD8-D91D10C69AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
